--- a/Paper/_output/_comparison/crisis_analysis_monthly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_monthly.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -454,8 +454,11 @@
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -541,12 +544,27 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>hit_count_full</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>hit_rate_ptt</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>hit_count_ptt</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>hit_rate_ttp</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>hit_count_ttp</t>
         </is>
       </c>
     </row>
@@ -603,8 +621,11 @@
         <v>0.1618545260524486</v>
       </c>
       <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -661,11 +682,26 @@
       <c r="P3" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="n">
         <v>0.5</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -723,11 +759,26 @@
       <c r="P4" s="2" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="n">
         <v>0.3333333333333333</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -785,11 +836,26 @@
       <c r="P5" s="2" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="n">
         <v>0.3333333333333333</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -847,12 +913,27 @@
       <c r="P6" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q6" s="2" t="n">
-        <v>0.5</v>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
       </c>
       <c r="R6" s="2" t="n">
         <v>0.5</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -909,11 +990,26 @@
       <c r="P7" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="n">
         <v>0.6666666666666666</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -971,11 +1067,26 @@
       <c r="P8" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q8" s="2" t="n">
-        <v>0.5</v>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
       </c>
       <c r="R8" s="2" t="n">
         <v>0.5</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Paper/_output/_comparison/crisis_analysis_monthly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_monthly.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -784,12 +784,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -798,40 +798,40 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>11.34247571880571</v>
+        <v>9.684634074996662</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.2395437510655433</v>
+        <v>-0.3416882532303288</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.4557974809248458</v>
+        <v>-0.3744774130256877</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1049030423631254</v>
+        <v>0.08522410333287994</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1717219263260847</v>
+        <v>0.1645222726818187</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9028685032661176</v>
+        <v>0.9096847486509514</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.09409780126747491</v>
+        <v>0.08846498007124048</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.4015568863218339</v>
+        <v>0.3877545076850768</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.5652819033224868</v>
+        <v>0.5454410266003107</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.206446514527776</v>
+        <v>0.2362358235613322</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1.295281120905988</v>
+        <v>0.8708733918691299</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>0.3333333333333333</v>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="T5" s="2" t="n">
@@ -861,12 +861,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -875,75 +875,75 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>14.77344973838645</v>
+        <v>11.34247571880571</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.02815134547656106</v>
+        <v>-0.2395437510655433</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.615775334514046</v>
+        <v>-0.4557974809248458</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1549269963941755</v>
+        <v>0.1049030423631254</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2167480726474567</v>
+        <v>0.1717219263260847</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9143709173530247</v>
+        <v>0.9028685032661176</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.1037434816583733</v>
+        <v>0.09409780126747491</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.3586471211757415</v>
+        <v>0.4015568863218339</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.5035077536386878</v>
+        <v>0.5652819033224868</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.168476189031256</v>
+        <v>0.206446514527776</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>5.494242384343042</v>
+        <v>1.295281120905988</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -952,47 +952,47 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>15.33705066887419</v>
+        <v>14.77344973838645</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.006573766345344012</v>
+        <v>-0.02815134547656106</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.6100001664268991</v>
+        <v>-0.615775334514046</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1598727964560844</v>
+        <v>0.1549269963941755</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2194950907957611</v>
+        <v>0.2167480726474567</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9157909684748651</v>
+        <v>0.9143709173530247</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.1051310191801103</v>
+        <v>0.1037434816583733</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.359883178229331</v>
+        <v>0.3586471211757415</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.5048658636092662</v>
+        <v>0.5035077536386878</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.1723458860608506</v>
+        <v>0.168476189031256</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>4.829376344876708</v>
+        <v>5.494242384343042</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="R7" s="2" t="n">
@@ -1004,23 +1004,23 @@
         </is>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1029,47 +1029,47 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>15.94681576629083</v>
+        <v>15.33705066887419</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.04414318833789377</v>
+        <v>0.006573766345344012</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.6146619938319895</v>
+        <v>-0.6100001664268991</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1667250989382133</v>
+        <v>0.1598727964560844</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2183672843667188</v>
+        <v>0.2194950907957611</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9152229480261289</v>
+        <v>0.9157909684748651</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.1065811609195164</v>
+        <v>0.1051310191801103</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.3677443608382825</v>
+        <v>0.359883178229331</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.5154333271220438</v>
+        <v>0.5048658636092662</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.1733980008346654</v>
+        <v>0.1723458860608506</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>3.360186480545662</v>
+        <v>4.829376344876708</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="R8" s="2" t="n">
@@ -1081,9 +1081,86 @@
         </is>
       </c>
       <c r="T8" s="2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>15.94681576629083</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.04414318833789377</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-0.6146619938319895</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.1667250989382133</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.2183672843667188</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0.9152229480261289</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0.1065811609195164</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.3677443608382825</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>0.5154333271220438</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>0.1733980008346654</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>3.360186480545662</v>
+      </c>
+      <c r="P9" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>3/6</t>
         </is>
@@ -1100,7 +1177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1404,12 +1481,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1418,60 +1495,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.3050913934539505</v>
+        <v>0.4662306966820124</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.4395948126489193</v>
+        <v>0.6173412189194043</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.3180206894883698</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1109469294357623</v>
+        <v>0.09188574888245429</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1530752451527519</v>
+        <v>0.1488918445234894</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9518005540166204</v>
+        <v>0.9418282548476454</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2627477773058103</v>
+        <v>-0.1630913374762594</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.3922472502781837</v>
+        <v>0.5804411953817679</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.5584925916461387</v>
+        <v>0.3466644120689842</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.3180206894883698</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.770210184900723</v>
+        <v>0.7519602345380432</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.03400801284489896</v>
+        <v>0.02334792565864707</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>1.081772824084672</v>
+        <v>1.056140469786753</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.1175306843923517</v>
+        <v>-0.1144491365988818</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1480,60 +1557,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.1727422704228461</v>
+        <v>0.3050913934539505</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.2936057179925118</v>
+        <v>0.4395948126489193</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.3857020660410981</v>
+        <v>-0.3432461105733071</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1401986532528675</v>
+        <v>0.1109469294357623</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1956510932256706</v>
+        <v>0.1530752451527519</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9722991689750693</v>
+        <v>0.9518005540166204</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.368727712232564</v>
+        <v>-0.2627477773058103</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.1921118441789917</v>
+        <v>0.3922472502781837</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.7837618941180758</v>
+        <v>0.5584925916461387</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.3857020660410981</v>
+        <v>-0.3432461105733071</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.8577439452797431</v>
+        <v>0.770210184900723</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.08513787889039803</v>
+        <v>0.03400801284489896</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.204715424720587</v>
+        <v>1.081772824084672</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1370443733149529</v>
+        <v>-0.1175306843923517</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1542,110 +1619,172 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.2064468322738722</v>
+        <v>0.1727422704228461</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.3307838900705071</v>
+        <v>0.2936057179925118</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.3957852429007654</v>
+        <v>-0.3857020660410981</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1429549412877313</v>
+        <v>0.1401986532528675</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2002183608269251</v>
+        <v>0.1956510932256706</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9706371191135734</v>
+        <v>0.9722991689750693</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.3754608976947176</v>
+        <v>-0.368727712232564</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.1793967126992393</v>
+        <v>0.1921118441789917</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.7980738484849268</v>
+        <v>0.7837618941180758</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.3957852429007654</v>
+        <v>-0.3857020660410981</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9317394664652177</v>
+        <v>0.8577439452797431</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.1283598434192632</v>
+        <v>0.08513787889039803</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.308643346593946</v>
+        <v>1.204715424720587</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1397690308849029</v>
+        <v>-0.1370443733149529</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.2064468322738722</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.3307838900705071</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-0.3957852429007654</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.1429549412877313</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.2002183608269251</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.9706371191135734</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.3754608976947176</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0.1793967126992393</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0.7980738484849268</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.3957852429007654</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.9317394664652177</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.1283598434192632</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>1.308643346593946</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-0.1397690308849029</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>lstm</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>0.2302139203155766</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>0.3570004269569067</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>-0.4221174890977989</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>0.1550900387558129</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.1953067267187089</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>0.968421052631579</v>
       </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="n">
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>-0.3976227638230778</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>0.137545638903235</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>0.8451807666733799</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>-0.4221174890977989</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>1.042264956961712</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>0.1929195458612629</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>1.463878208884358</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>-0.1348418208118199</v>
       </c>
     </row>
@@ -1660,7 +1799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1964,12 +2103,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1978,60 +2117,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.2553938843122963</v>
+        <v>0.4214855010465173</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.1911821718000761</v>
+        <v>0.3487784252242632</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.3744774130256878</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1742196764528615</v>
+        <v>0.1200249121443981</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.2118070551778035</v>
+        <v>0.200292846208758</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9491279069767442</v>
+        <v>0.9244186046511628</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.4557974809248456</v>
+        <v>-0.3743492138682257</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.09609800828525117</v>
+        <v>0.2601459135591284</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.9052415190749453</v>
+        <v>0.7434803069533858</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.3744774130256878</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1.306850557115716</v>
+        <v>1.272011052419783</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.08674786633685749</v>
+        <v>0.07033511810930126</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>1.164014361496109</v>
+        <v>1.132982746142185</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.1243810385007439</v>
+        <v>-0.1172230559518105</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2040,60 +2179,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.03069342544864184</v>
+        <v>0.2553938843122963</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.08027215598020898</v>
+        <v>0.1911821718000761</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.6157753345140465</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.2834217467647488</v>
+        <v>0.1742196764528615</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2902475246683776</v>
+        <v>0.2118070551778035</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
+        <v>0.9491279069767442</v>
       </c>
       <c r="J6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.6131881355073265</v>
+        <v>-0.4557974809248456</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.2209082108402154</v>
+        <v>0.09609800828525117</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.217828931698091</v>
+        <v>0.9052415190749453</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.6157753345140465</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1.50588635853417</v>
+        <v>1.306850557115716</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.1805128186650207</v>
+        <v>0.08674786633685749</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.341295941276967</v>
+        <v>1.164014361496109</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1991621896471399</v>
+        <v>-0.1243810385007439</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2102,19 +2241,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.05847752440067311</v>
+        <v>-0.03069342544864184</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.1066351355555943</v>
+        <v>-0.08027215598020898</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.6100001664268992</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.2927826980910351</v>
+        <v>0.2834217467647488</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2857263117276639</v>
+        <v>0.2902475246683776</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>1</v>
@@ -2123,39 +2262,39 @@
         <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.6055610031715249</v>
+        <v>-0.6131881355073265</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.205546127297479</v>
+        <v>-0.2209082108402154</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.202680982991053</v>
+        <v>1.217828931698091</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.6100001664268992</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1.386991355240556</v>
+        <v>1.50588635853417</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.1245018686930377</v>
+        <v>0.1805128186650207</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.23539592800434</v>
+        <v>1.341295941276967</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1935283927621277</v>
+        <v>-0.1991621896471399</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2164,19 +2303,19 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.07923416091300595</v>
+        <v>-0.05847752440067311</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.1263300979645993</v>
+        <v>-0.1066351355555943</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.6146619938319893</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.3064991258757455</v>
+        <v>0.2927826980910351</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2922276320458878</v>
+        <v>0.2857263117276639</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>1</v>
@@ -2185,27 +2324,89 @@
         <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
+        <v>-0.6055610031715249</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.205546127297479</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>1.202680982991053</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.6100001664268992</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>1.386991355240556</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.1245018686930377</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>1.23539592800434</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-0.1935283927621277</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>-0.07923416091300595</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>-0.1263300979645993</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-0.6146619938319893</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.3064991258757455</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.2922276320458878</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>-0.6131081926512691</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>-0.2207471950377711</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>1.217670160323774</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>-0.6146619938319893</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>1.379905238616354</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>0.1211636281216184</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>1.229084309990409</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>-0.2037181450170952</v>
       </c>
     </row>
@@ -2220,7 +2421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2524,12 +2725,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2538,60 +2739,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.0189637709832835</v>
+        <v>0.001802582320870938</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.004344397865602034</v>
+        <v>-0.0211130349041182</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.143729669862375</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.04520489920804412</v>
+        <v>0.04690988384817812</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.165114162844639</v>
+        <v>0.153917301860116</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9448275862068966</v>
+        <v>0.9862068965517241</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.1360620360985055</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.06570035000010499</v>
+        <v>0.07379760643682176</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.7295286224594077</v>
+        <v>0.696194308369228</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.143729669862375</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.1884023656024003</v>
+        <v>0.1595769883716971</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.06572649419295029</v>
+        <v>-0.08838783097671599</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.6926381315189625</v>
+        <v>0.586665176447165</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.02128572850164578</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2600,60 +2801,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.03113418626728315</v>
+        <v>0.0189637709832835</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.007547626662535167</v>
+        <v>-0.004344397865602034</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.1452798889626855</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.05957889510636127</v>
+        <v>0.04520489920804412</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1870865456402408</v>
+        <v>0.165114162844639</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9379310344827586</v>
+        <v>0.9448275862068966</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.1425767900867722</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.01865603812212591</v>
+        <v>0.06570035000010499</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.9231979079208384</v>
+        <v>0.7295286224594077</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.1452798889626855</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.2581357263948778</v>
+        <v>0.1884023656024003</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.01090496796157892</v>
+        <v>-0.06572649419295029</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.9490042581830531</v>
+        <v>0.6926381315189625</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.0280449453540883</v>
+        <v>-0.02330447460112961</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2662,110 +2863,172 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.05464279041512032</v>
+        <v>0.03113418626728315</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.03051848596557694</v>
+        <v>0.007547626662535167</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.1804269089298145</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.05565303537278199</v>
+        <v>0.05957889510636127</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.1949988330089462</v>
+        <v>0.1870865456402408</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.896551724137931</v>
+        <v>0.9379310344827586</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.1756429698727684</v>
+        <v>-0.1804269089298145</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.02460204642762664</v>
+        <v>0.01865603812212591</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.8987197269483773</v>
+        <v>0.9231979079208384</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.1804269089298145</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.279351969925393</v>
+        <v>0.2581357263948778</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.005774378021768278</v>
+        <v>-0.01090496796157892</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.027003168811594</v>
+        <v>0.9490042581830531</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.02998688672969829</v>
+        <v>-0.0280449453540883</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.05464279041512032</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.03051848596557694</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-0.1758389292270287</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.05565303537278199</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.1949988330089462</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.896551724137931</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.1756429698727684</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0.02460204642762664</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0.8987197269483773</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.1758389292270287</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.279351969925393</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.005774378021768278</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>1.027003168811594</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-0.02998688672969829</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>lstm</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>0.05461060122071615</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>0.03048703307917489</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>-0.161539993759288</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>0.04772879566569357</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.1794422862086121</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>0.8689655172413793</v>
       </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="n">
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>-0.161539993759288</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>0.0421307841692844</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>0.8265584394738612</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>-0.161539993759288</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>0.2577947586899569</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>-0.01117302287485056</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>0.9477507323406914</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>-0.0232535172924333</v>
       </c>
     </row>
@@ -2780,7 +3043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3084,12 +3347,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3098,60 +3361,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-0.0009544101684616502</v>
+        <v>0.0001327025339010746</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.08997859384708495</v>
+        <v>-0.08898835292102503</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1202708276706985</v>
+        <v>0.1193940004707371</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.428252010780779</v>
+        <v>0.4109397789559724</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>0.9918032786885246</v>
       </c>
       <c r="J5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.00807433626786469</v>
+        <v>0.00124772041103749</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.019747133566668</v>
+        <v>0.9969484920130616</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.2893340076613283</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.4189993189650008</v>
+        <v>0.4073175209111213</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.08257096330288938</v>
+        <v>-0.09012362424657316</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.7663973627717755</v>
+        <v>0.7450300267984358</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.07538615706116925</v>
+        <v>-0.0790522597965585</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3160,60 +3423,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.004064398596093755</v>
+        <v>-0.0009544101684616502</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.08540700726923578</v>
+        <v>-0.08997859384708495</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1330355594692814</v>
+        <v>0.1202708276706985</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.4884782875332566</v>
+        <v>0.428252010780779</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>1</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.04551457597582553</v>
+        <v>-0.00807433626786469</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.111313472861166</v>
+        <v>1.019747133566668</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.4820684921877625</v>
+        <v>0.4189993189650008</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.04179469931056778</v>
+        <v>-0.08257096330288938</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.8817580467688738</v>
+        <v>0.7663973627717755</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.09007578809896477</v>
+        <v>-0.07538615706116925</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3222,60 +3485,60 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.03121918450036776</v>
+        <v>0.004064398596093755</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.1175464974290086</v>
+        <v>-0.08540700726923578</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1525896620499075</v>
+        <v>0.1330355594692814</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.507010924502074</v>
+        <v>0.4884782875332566</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
+        <v>0.9918032786885246</v>
       </c>
       <c r="J7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.07186081874535022</v>
+        <v>-0.04551457597582553</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.175747595702974</v>
+        <v>1.111313472861166</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.4705792374445794</v>
+        <v>0.4820684921877625</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.04922287476529197</v>
+        <v>-0.04179469931056778</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.8607428943883418</v>
+        <v>0.8817580467688738</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.09590060655538413</v>
+        <v>-0.09007578809896477</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lstm</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lstm_t_10_holdout_rank</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3284,19 +3547,19 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.00261610496364173</v>
+        <v>-0.03121918450036776</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.09149221629784987</v>
+        <v>-0.1175464974290086</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.3207580395918463</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1344899709337924</v>
+        <v>0.1525896620499075</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.4858267016059757</v>
+        <v>0.507010924502074</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>1</v>
@@ -3305,27 +3568,89 @@
         <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
+        <v>-0.341225014720676</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.07186081874535022</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>1.175747595702974</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.341225014720676</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.4705792374445794</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>-0.04922287476529197</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.8607428943883418</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-0.09590060655538413</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>-0.00261610496364173</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>-0.09149221629784987</v>
+      </c>
+      <c r="F9" s="2" t="n">
         <v>-0.3207580395918463</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="G9" s="2" t="n">
+        <v>0.1344899709337924</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.4858267016059757</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>-0.3207580395918463</v>
+      </c>
+      <c r="L9" s="2" t="n">
         <v>-0.04302517385398152</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>1.105225225534033</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>-0.3207580395918463</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>0.468377917107822</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>-0.05064609968796929</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>0.8567164293695581</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>-0.09945162290284171</v>
       </c>
     </row>
@@ -3340,7 +3665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3644,12 +3969,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3658,60 +3983,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.05550959933794908</v>
+        <v>-0.01525424958956756</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.005190714109256422</v>
+        <v>-0.07188507109342634</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.2223141762956242</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1161134555088488</v>
+        <v>0.121880142964137</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1734081721485486</v>
+        <v>0.1646297036067336</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9727095516569201</v>
+        <v>1</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2377598766809244</v>
+        <v>-0.2202351424839316</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.1044258367867865</v>
+        <v>0.1298177948297481</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.7673849036436503</v>
+        <v>0.7108227256560352</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.2223141762956242</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.3847468363930642</v>
+        <v>0.2628752641499237</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.09925207039248651</v>
+        <v>-0.1785268977406829</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.7160345022383415</v>
+        <v>0.489224968503877</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.07769789874505417</v>
+        <v>-0.09340275911067697</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3720,60 +4045,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.1265525925696835</v>
+        <v>0.05550959933794908</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.06176673413065714</v>
+        <v>-0.005190714109256422</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.3287615049188402</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1723102832459509</v>
+        <v>0.1161134555088488</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2353745170087453</v>
+        <v>0.1734081721485486</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9512670565302144</v>
+        <v>0.9727095516569201</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.3283422830072888</v>
+        <v>-0.2377598766809244</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.0268209276442668</v>
+        <v>0.1044258367867865</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.059745297335527</v>
+        <v>0.7673849036436503</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.3283422830072888</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.6772718664109521</v>
+        <v>0.3847468363930642</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.09102914796604056</v>
+        <v>-0.09925207039248651</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.260439275581632</v>
+        <v>0.7160345022383415</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1055180017892465</v>
+        <v>-0.07769789874505417</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3782,19 +4107,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.1385354644109973</v>
+        <v>0.1265525925696835</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.07306049421285321</v>
+        <v>0.06176673413065714</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.3381261530483139</v>
+        <v>-0.3287615049188402</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1790388907472599</v>
+        <v>0.1723102832459509</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2472263231475021</v>
+        <v>0.2353745170087453</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>0.9512670565302144</v>
@@ -3803,89 +4128,151 @@
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.3372034926825385</v>
+        <v>-0.3283422830072888</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.03966012176582068</v>
+        <v>-0.0268209276442668</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.088345406940788</v>
+        <v>1.059745297335527</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.3372034926825385</v>
+        <v>-0.3283422830072888</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.7177752927802767</v>
+        <v>0.6772718664109521</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.1173757526199353</v>
+        <v>0.09102914796604056</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.335818324857759</v>
+        <v>1.260439275581632</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1166039321461161</v>
+        <v>-0.1055180017892465</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.1385354644109973</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.07306049421285321</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-0.3381261530483139</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.1790388907472599</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.2472263231475021</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.9512670565302144</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.3372034926825385</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.03966012176582068</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>1.088345406940788</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.3372034926825385</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.7177752927802767</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.1173757526199353</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>1.335818324857759</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-0.1166039321461161</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>lstm</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>0.171220671088737</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>0.1038660379375795</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>-0.3380397400935387</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>0.1740509194643686</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.2513047692917923</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I9" s="2" t="n">
         <v>0.9317738791423001</v>
       </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="n">
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>-0.3340616179283677</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>-0.03510779298083788</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>1.078204809253966</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>-0.3340616179283675</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>0.7587523149593043</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>0.1440304211262609</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>1.41207876134175</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>-0.1136737333480079</v>
       </c>
     </row>
@@ -3900,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4204,12 +4591,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>mvo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>mvo_t_10_lw_minvar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4218,19 +4605,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-0.04941120899711726</v>
+        <v>-0.06676653353273054</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.04712810219865582</v>
+        <v>-0.06452511043579368</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.1208786768201607</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.07294179359961758</v>
+        <v>0.06599576241334662</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.2326154609655196</v>
+        <v>0.2156952619322512</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>1</v>
@@ -4239,39 +4626,39 @@
         <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.1208786768201607</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.09388774724005255</v>
+        <v>0.13318215211393</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.6751222101795875</v>
+        <v>0.5391526104926985</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.1208786768201607</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.1201362258412626</v>
+        <v>0.06155253189821752</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.1289125413411937</v>
+        <v>-0.1744708581765999</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.4201954534641747</v>
+        <v>0.2152897169169782</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.04770980148098947</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4280,19 +4667,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.01500324256968033</v>
+        <v>-0.04941120899711726</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.01263749534581593</v>
+        <v>-0.04712810219865582</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.1891226670882522</v>
+        <v>-0.1513632279065376</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.09328475897205027</v>
+        <v>0.07294179359961758</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.3054222199740849</v>
+        <v>0.2326154609655196</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1</v>
@@ -4301,39 +4688,39 @@
         <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1891226670882522</v>
+        <v>-0.1513632279065376</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.04521605491915381</v>
+        <v>0.09388774724005255</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.8435398396664642</v>
+        <v>0.6751222101795875</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.1891226670882522</v>
+        <v>-0.1513632279065376</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.214729672974497</v>
+        <v>0.1201362258412626</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.05535080521648206</v>
+        <v>-0.1289125413411937</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.7510509979475514</v>
+        <v>0.4201954534641747</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.08996647052893747</v>
+        <v>-0.04910852885624428</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4342,110 +4729,172 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.009474010358029972</v>
+        <v>-0.01500324256968033</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.01189854660096956</v>
+        <v>-0.01263749534581593</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.1965679708822623</v>
+        <v>-0.1891226670882522</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.09228683758884382</v>
+        <v>0.09328475897205027</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.3142199894496041</v>
+        <v>0.3054222199740849</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9772727272727273</v>
+        <v>1</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.1965679708822623</v>
+        <v>-0.1891226670882522</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.03561910265103974</v>
+        <v>0.04521605491915381</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.8767479710097934</v>
+        <v>0.8435398396664642</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.1965679708822623</v>
+        <v>-0.1891226670882522</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.2564522869054031</v>
+        <v>0.214729672974497</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.02290471080472434</v>
+        <v>-0.05535080521648206</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.8969824400054414</v>
+        <v>0.7510509979475514</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.08406739461942148</v>
+        <v>-0.08996647052893747</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.009474010358029972</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.01189854660096956</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-0.1965679708822623</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.09228683758884382</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.3142199894496041</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.9772727272727273</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.1965679708822623</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0.03561910265103974</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0.8767479710097934</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.1965679708822623</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.2564522869054031</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>-0.02290471080472434</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.8969824400054414</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-0.08406739461942148</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>lstm</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>-0.01216599018987663</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E9" s="2" t="n">
         <v>-0.009793428505060708</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>-0.1711634614757399</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>0.0826181758453077</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.2821735006319364</v>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="b">
+      <c r="I9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="b">
         <v>0</v>
       </c>
-      <c r="K8" s="2" t="n">
+      <c r="K9" s="2" t="n">
         <v>-0.1711634614757399</v>
       </c>
-      <c r="L8" s="2" t="n">
+      <c r="L9" s="2" t="n">
         <v>0.06836536404139437</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M9" s="3" t="n">
         <v>0.763436773988745</v>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N9" s="2" t="n">
         <v>-0.1711634614757399</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O9" s="2" t="n">
         <v>0.1918321211670491</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>-0.07315736280592</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q9" s="3" t="n">
         <v>0.6709631884831277</v>
       </c>
-      <c r="R8" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>-0.07691029042613784</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_monthly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_monthly.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -784,12 +784,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -798,40 +798,40 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9.684634074996662</v>
+        <v>11.34247571880571</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.3416882532303288</v>
+        <v>-0.2395437510655433</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.3744774130256877</v>
+        <v>-0.4557974809248458</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.08522410333287994</v>
+        <v>0.1049030423631254</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1645222726818187</v>
+        <v>0.1717219263260847</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9096847486509514</v>
+        <v>0.9028685032661176</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.08846498007124048</v>
+        <v>0.09409780126747491</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.3877545076850768</v>
+        <v>0.4015568863218339</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.5454410266003107</v>
+        <v>0.5652819033224868</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.2362358235613322</v>
+        <v>0.206446514527776</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.8708733918691299</v>
+        <v>1.295281120905988</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>0.3333333333333333</v>
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="R5" s="2" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="T5" s="2" t="n">
@@ -861,12 +861,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -875,75 +875,75 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>11.34247571880571</v>
+        <v>14.77344973838645</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.2395437510655433</v>
+        <v>-0.02815134547656106</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.4557974809248458</v>
+        <v>-0.615775334514046</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1049030423631254</v>
+        <v>0.1549269963941755</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1717219263260847</v>
+        <v>0.2167480726474567</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9028685032661176</v>
+        <v>0.9143709173530247</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.09409780126747491</v>
+        <v>0.1037434816583733</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.4015568863218339</v>
+        <v>0.3586471211757415</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.5652819033224868</v>
+        <v>0.5035077536386878</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.206446514527776</v>
+        <v>0.168476189031256</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1.295281120905988</v>
+        <v>5.494242384343042</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -952,47 +952,47 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>14.77344973838645</v>
+        <v>15.33705066887419</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.02815134547656106</v>
+        <v>0.006573766345344012</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.615775334514046</v>
+        <v>-0.6100001664268991</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1549269963941755</v>
+        <v>0.1598727964560844</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2167480726474567</v>
+        <v>0.2194950907957611</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9143709173530247</v>
+        <v>0.9157909684748651</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.1037434816583733</v>
+        <v>0.1051310191801103</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.3586471211757415</v>
+        <v>0.359883178229331</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.5035077536386878</v>
+        <v>0.5048658636092662</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.168476189031256</v>
+        <v>0.1723458860608506</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>5.494242384343042</v>
+        <v>4.829376344876708</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="R7" s="2" t="n">
@@ -1004,23 +1004,23 @@
         </is>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1029,47 +1029,47 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>15.33705066887419</v>
+        <v>15.94681576629083</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.006573766345344012</v>
+        <v>0.04414318833789377</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.6100001664268991</v>
+        <v>-0.6146619938319895</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1598727964560844</v>
+        <v>0.1667250989382133</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2194950907957611</v>
+        <v>0.2183672843667188</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9157909684748651</v>
+        <v>0.9152229480261289</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.1051310191801103</v>
+        <v>0.1065811609195164</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.359883178229331</v>
+        <v>0.3677443608382825</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.5048658636092662</v>
+        <v>0.5154333271220438</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.1723458860608506</v>
+        <v>0.1733980008346654</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>4.829376344876708</v>
+        <v>3.360186480545662</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="R8" s="2" t="n">
@@ -1081,86 +1081,9 @@
         </is>
       </c>
       <c r="T8" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="U8" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>15.94681576629083</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.04414318833789377</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-0.6146619938319895</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.1667250989382133</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.2183672843667188</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0.9152229480261289</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0.1065811609195164</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.3677443608382825</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>0.5154333271220438</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>0.1733980008346654</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>3.360186480545662</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U9" t="inlineStr">
         <is>
           <t>3/6</t>
         </is>
@@ -1177,7 +1100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1481,12 +1404,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1495,60 +1418,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.4662306966820124</v>
+        <v>0.3050913934539505</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.6173412189194043</v>
+        <v>0.4395948126489193</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.3180206894883698</v>
+        <v>-0.3432461105733071</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.09188574888245429</v>
+        <v>0.1109469294357623</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1488918445234894</v>
+        <v>0.1530752451527519</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9418282548476454</v>
+        <v>0.9518005540166204</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.1630913374762594</v>
+        <v>-0.2627477773058103</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.5804411953817679</v>
+        <v>0.3922472502781837</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.3466644120689842</v>
+        <v>0.5584925916461387</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.3180206894883698</v>
+        <v>-0.3432461105733071</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.7519602345380432</v>
+        <v>0.770210184900723</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.02334792565864707</v>
+        <v>0.03400801284489896</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>1.056140469786753</v>
+        <v>1.081772824084672</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.1144491365988818</v>
+        <v>-0.1175306843923517</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1557,60 +1480,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.3050913934539505</v>
+        <v>0.1727422704228461</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.4395948126489193</v>
+        <v>0.2936057179925118</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.3857020660410981</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1109469294357623</v>
+        <v>0.1401986532528675</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1530752451527519</v>
+        <v>0.1956510932256706</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9518005540166204</v>
+        <v>0.9722991689750693</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.2627477773058103</v>
+        <v>-0.368727712232564</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.3922472502781837</v>
+        <v>0.1921118441789917</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.5584925916461387</v>
+        <v>0.7837618941180758</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.3857020660410981</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.770210184900723</v>
+        <v>0.8577439452797431</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.03400801284489896</v>
+        <v>0.08513787889039803</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.081772824084672</v>
+        <v>1.204715424720587</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1175306843923517</v>
+        <v>-0.1370443733149529</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1619,60 +1542,60 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.1727422704228461</v>
+        <v>0.2064468322738722</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.2936057179925118</v>
+        <v>0.3307838900705071</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.3857020660410981</v>
+        <v>-0.3957852429007654</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1401986532528675</v>
+        <v>0.1429549412877313</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.1956510932256706</v>
+        <v>0.2002183608269251</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9722991689750693</v>
+        <v>0.9706371191135734</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.368727712232564</v>
+        <v>-0.3754608976947176</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.1921118441789917</v>
+        <v>0.1793967126992393</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.7837618941180758</v>
+        <v>0.7980738484849268</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.3857020660410981</v>
+        <v>-0.3957852429007654</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.8577439452797431</v>
+        <v>0.9317394664652177</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.08513787889039803</v>
+        <v>0.1283598434192632</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.204715424720587</v>
+        <v>1.308643346593946</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1370443733149529</v>
+        <v>-0.1397690308849029</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1681,110 +1604,48 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.2064468322738722</v>
+        <v>0.2302139203155766</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.3307838900705071</v>
+        <v>0.3570004269569067</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.3957852429007654</v>
+        <v>-0.4221174890977989</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1429549412877313</v>
+        <v>0.1550900387558129</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2002183608269251</v>
+        <v>0.1953067267187089</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9706371191135734</v>
+        <v>0.968421052631579</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.3754608976947176</v>
+        <v>-0.3976227638230778</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.1793967126992393</v>
+        <v>0.137545638903235</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.7980738484849268</v>
+        <v>0.8451807666733799</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.3957852429007654</v>
+        <v>-0.4221174890977989</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.9317394664652177</v>
+        <v>1.042264956961712</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.1283598434192632</v>
+        <v>0.1929195458612629</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.308643346593946</v>
+        <v>1.463878208884358</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.1397690308849029</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0.2302139203155766</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.3570004269569067</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-0.4221174890977989</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.1550900387558129</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.1953067267187089</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0.968421052631579</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>-0.3976227638230778</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0.137545638903235</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>0.8451807666733799</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>-0.4221174890977989</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>1.042264956961712</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>0.1929195458612629</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>1.463878208884358</v>
-      </c>
-      <c r="R9" s="2" t="n">
         <v>-0.1348418208118199</v>
       </c>
     </row>
@@ -1799,7 +1660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2103,12 +1964,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2117,60 +1978,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.4214855010465173</v>
+        <v>0.2553938843122963</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.3487784252242632</v>
+        <v>0.1911821718000761</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1200249121443981</v>
+        <v>0.1742196764528615</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.200292846208758</v>
+        <v>0.2118070551778035</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9244186046511628</v>
+        <v>0.9491279069767442</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.3743492138682257</v>
+        <v>-0.4557974809248456</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.2601459135591284</v>
+        <v>0.09609800828525117</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.7434803069533858</v>
+        <v>0.9052415190749453</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.3744774130256878</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1.272011052419783</v>
+        <v>1.306850557115716</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.07033511810930126</v>
+        <v>0.08674786633685749</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>1.132982746142185</v>
+        <v>1.164014361496109</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.1172230559518105</v>
+        <v>-0.1243810385007439</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2179,60 +2040,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.2553938843122963</v>
+        <v>-0.03069342544864184</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.1911821718000761</v>
+        <v>-0.08027215598020898</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1742196764528615</v>
+        <v>0.2834217467647488</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2118070551778035</v>
+        <v>0.2902475246683776</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9491279069767442</v>
+        <v>1</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.4557974809248456</v>
+        <v>-0.6131881355073265</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.09609800828525117</v>
+        <v>-0.2209082108402154</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.9052415190749453</v>
+        <v>1.217828931698091</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1.306850557115716</v>
+        <v>1.50588635853417</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.08674786633685749</v>
+        <v>0.1805128186650207</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.164014361496109</v>
+        <v>1.341295941276967</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1243810385007439</v>
+        <v>-0.1991621896471399</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2241,19 +2102,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.03069342544864184</v>
+        <v>-0.05847752440067311</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.08027215598020898</v>
+        <v>-0.1066351355555943</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.6157753345140465</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.2834217467647488</v>
+        <v>0.2927826980910351</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2902475246683776</v>
+        <v>0.2857263117276639</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>1</v>
@@ -2262,39 +2123,39 @@
         <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.6131881355073265</v>
+        <v>-0.6055610031715249</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.2209082108402154</v>
+        <v>-0.205546127297479</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.217828931698091</v>
+        <v>1.202680982991053</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.6157753345140465</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1.50588635853417</v>
+        <v>1.386991355240556</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.1805128186650207</v>
+        <v>0.1245018686930377</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.341295941276967</v>
+        <v>1.23539592800434</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1991621896471399</v>
+        <v>-0.1935283927621277</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2303,19 +2164,19 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.05847752440067311</v>
+        <v>-0.07923416091300595</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.1066351355555943</v>
+        <v>-0.1263300979645993</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.6100001664268992</v>
+        <v>-0.6146619938319893</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.2927826980910351</v>
+        <v>0.3064991258757455</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2857263117276639</v>
+        <v>0.2922276320458878</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>1</v>
@@ -2324,89 +2185,27 @@
         <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.6055610031715249</v>
+        <v>-0.6131081926512691</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.205546127297479</v>
+        <v>-0.2207471950377711</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.202680982991053</v>
+        <v>1.217670160323774</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.6100001664268992</v>
+        <v>-0.6146619938319893</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1.386991355240556</v>
+        <v>1.379905238616354</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.1245018686930377</v>
+        <v>0.1211636281216184</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.23539592800434</v>
+        <v>1.229084309990409</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.1935283927621277</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>-0.07923416091300595</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>-0.1263300979645993</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-0.6146619938319893</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.3064991258757455</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.2922276320458878</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>-0.6131081926512691</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>-0.2207471950377711</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>1.217670160323774</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>-0.6146619938319893</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>1.379905238616354</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>0.1211636281216184</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>1.229084309990409</v>
-      </c>
-      <c r="R9" s="2" t="n">
         <v>-0.2037181450170952</v>
       </c>
     </row>
@@ -2421,7 +2220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2725,12 +2524,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2739,60 +2538,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.001802582320870938</v>
+        <v>0.0189637709832835</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.0211130349041182</v>
+        <v>-0.004344397865602034</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.143729669862375</v>
+        <v>-0.1452798889626855</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.04690988384817812</v>
+        <v>0.04520489920804412</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.153917301860116</v>
+        <v>0.165114162844639</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.9448275862068966</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.1360620360985055</v>
+        <v>-0.1425767900867722</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.07379760643682176</v>
+        <v>0.06570035000010499</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.696194308369228</v>
+        <v>0.7295286224594077</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.143729669862375</v>
+        <v>-0.1452798889626855</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.1595769883716971</v>
+        <v>0.1884023656024003</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.08838783097671599</v>
+        <v>-0.06572649419295029</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.586665176447165</v>
+        <v>0.6926381315189625</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.02128572850164578</v>
+        <v>-0.02330447460112961</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2801,60 +2600,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.0189637709832835</v>
+        <v>0.03113418626728315</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.004344397865602034</v>
+        <v>0.007547626662535167</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.1804269089298145</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.04520489920804412</v>
+        <v>0.05957889510636127</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.165114162844639</v>
+        <v>0.1870865456402408</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9448275862068966</v>
+        <v>0.9379310344827586</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.1804269089298145</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.06570035000010499</v>
+        <v>0.01865603812212591</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.7295286224594077</v>
+        <v>0.9231979079208384</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.1804269089298145</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.1884023656024003</v>
+        <v>0.2581357263948778</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.06572649419295029</v>
+        <v>-0.01090496796157892</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.6926381315189625</v>
+        <v>0.9490042581830531</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.0280449453540883</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2863,60 +2662,60 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.03113418626728315</v>
+        <v>0.05464279041512032</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.007547626662535167</v>
+        <v>0.03051848596557694</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.1758389292270287</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.05957889510636127</v>
+        <v>0.05565303537278199</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.1870865456402408</v>
+        <v>0.1949988330089462</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9379310344827586</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.1756429698727684</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.01865603812212591</v>
+        <v>0.02460204642762664</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.9231979079208384</v>
+        <v>0.8987197269483773</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.1758389292270287</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.2581357263948778</v>
+        <v>0.279351969925393</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.01090496796157892</v>
+        <v>0.005774378021768278</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.9490042581830531</v>
+        <v>1.027003168811594</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.0280449453540883</v>
+        <v>-0.02998688672969829</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2925,110 +2724,48 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.05464279041512032</v>
+        <v>0.05461060122071615</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.03051848596557694</v>
+        <v>0.03048703307917489</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.161539993759288</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.05565303537278199</v>
+        <v>0.04772879566569357</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.1949988330089462</v>
+        <v>0.1794422862086121</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.896551724137931</v>
+        <v>0.8689655172413793</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.1756429698727684</v>
+        <v>-0.161539993759288</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.02460204642762664</v>
+        <v>0.0421307841692844</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.8987197269483773</v>
+        <v>0.8265584394738612</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.161539993759288</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.279351969925393</v>
+        <v>0.2577947586899569</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.005774378021768278</v>
+        <v>-0.01117302287485056</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.027003168811594</v>
+        <v>0.9477507323406914</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.02998688672969829</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0.05461060122071615</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.03048703307917489</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-0.161539993759288</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.04772879566569357</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.1794422862086121</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0.8689655172413793</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>-0.161539993759288</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0.0421307841692844</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>0.8265584394738612</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>-0.161539993759288</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0.2577947586899569</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>-0.01117302287485056</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.9477507323406914</v>
-      </c>
-      <c r="R9" s="2" t="n">
         <v>-0.0232535172924333</v>
       </c>
     </row>
@@ -3043,7 +2780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3347,12 +3084,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3361,60 +3098,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.0001327025339010746</v>
+        <v>-0.0009544101684616502</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.08898835292102503</v>
+        <v>-0.08997859384708495</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1193940004707371</v>
+        <v>0.1202708276706985</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.4109397789559724</v>
+        <v>0.428252010780779</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>1</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.00124772041103749</v>
+        <v>-0.00807433626786469</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.9969484920130616</v>
+        <v>1.019747133566668</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.2893340076613283</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.4073175209111213</v>
+        <v>0.4189993189650008</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.09012362424657316</v>
+        <v>-0.08257096330288938</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.7450300267984358</v>
+        <v>0.7663973627717755</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.0790522597965585</v>
+        <v>-0.07538615706116925</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3423,60 +3160,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.0009544101684616502</v>
+        <v>0.004064398596093755</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.08997859384708495</v>
+        <v>-0.08540700726923578</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1202708276706985</v>
+        <v>0.1330355594692814</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.428252010780779</v>
+        <v>0.4884782875332566</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
+        <v>0.9918032786885246</v>
       </c>
       <c r="J6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.00807433626786469</v>
+        <v>-0.04551457597582553</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.019747133566668</v>
+        <v>1.111313472861166</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.4189993189650008</v>
+        <v>0.4820684921877625</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.08257096330288938</v>
+        <v>-0.04179469931056778</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.7663973627717755</v>
+        <v>0.8817580467688738</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.07538615706116925</v>
+        <v>-0.09007578809896477</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3485,60 +3222,60 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.004064398596093755</v>
+        <v>-0.03121918450036776</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.08540700726923578</v>
+        <v>-0.1175464974290086</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1330355594692814</v>
+        <v>0.1525896620499075</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.4884782875332566</v>
+        <v>0.507010924502074</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>1</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.04551457597582553</v>
+        <v>-0.07186081874535022</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.111313472861166</v>
+        <v>1.175747595702974</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.4820684921877625</v>
+        <v>0.4705792374445794</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.04179469931056778</v>
+        <v>-0.04922287476529197</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.8817580467688738</v>
+        <v>0.8607428943883418</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.09007578809896477</v>
+        <v>-0.09590060655538413</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3547,19 +3284,19 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.03121918450036776</v>
+        <v>-0.00261610496364173</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.1175464974290086</v>
+        <v>-0.09149221629784987</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.3207580395918463</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1525896620499075</v>
+        <v>0.1344899709337924</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.507010924502074</v>
+        <v>0.4858267016059757</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>1</v>
@@ -3568,89 +3305,27 @@
         <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.3207580395918463</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.07186081874535022</v>
+        <v>-0.04302517385398152</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.175747595702974</v>
+        <v>1.105225225534033</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.3207580395918463</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.4705792374445794</v>
+        <v>0.468377917107822</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>-0.04922287476529197</v>
+        <v>-0.05064609968796929</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.8607428943883418</v>
+        <v>0.8567164293695581</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.09590060655538413</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>-0.00261610496364173</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>-0.09149221629784987</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-0.3207580395918463</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.1344899709337924</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.4858267016059757</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>-0.3207580395918463</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>-0.04302517385398152</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>1.105225225534033</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>-0.3207580395918463</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0.468377917107822</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>-0.05064609968796929</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.8567164293695581</v>
-      </c>
-      <c r="R9" s="2" t="n">
         <v>-0.09945162290284171</v>
       </c>
     </row>
@@ -3665,7 +3340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3969,12 +3644,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3983,60 +3658,60 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-0.01525424958956756</v>
+        <v>0.05550959933794908</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.07188507109342634</v>
+        <v>-0.005190714109256422</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.2223141762956242</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.121880142964137</v>
+        <v>0.1161134555088488</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1646297036067336</v>
+        <v>0.1734081721485486</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>0.9727095516569201</v>
       </c>
       <c r="J5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2202351424839316</v>
+        <v>-0.2377598766809244</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.1298177948297481</v>
+        <v>0.1044258367867865</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.7108227256560352</v>
+        <v>0.7673849036436503</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.2223141762956242</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.2628752641499237</v>
+        <v>0.3847468363930642</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.1785268977406829</v>
+        <v>-0.09925207039248651</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.489224968503877</v>
+        <v>0.7160345022383415</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.09340275911067697</v>
+        <v>-0.07769789874505417</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4045,60 +3720,60 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.05550959933794908</v>
+        <v>0.1265525925696835</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.005190714109256422</v>
+        <v>0.06176673413065714</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.3287615049188402</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1161134555088488</v>
+        <v>0.1723102832459509</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1734081721485486</v>
+        <v>0.2353745170087453</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9727095516569201</v>
+        <v>0.9512670565302144</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.2377598766809244</v>
+        <v>-0.3283422830072888</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.1044258367867865</v>
+        <v>-0.0268209276442668</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.7673849036436503</v>
+        <v>1.059745297335527</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.3283422830072888</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.3847468363930642</v>
+        <v>0.6772718664109521</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.09925207039248651</v>
+        <v>0.09102914796604056</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.7160345022383415</v>
+        <v>1.260439275581632</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.07769789874505417</v>
+        <v>-0.1055180017892465</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4107,19 +3782,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.1265525925696835</v>
+        <v>0.1385354644109973</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.06176673413065714</v>
+        <v>0.07306049421285321</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.3287615049188402</v>
+        <v>-0.3381261530483139</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1723102832459509</v>
+        <v>0.1790388907472599</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2353745170087453</v>
+        <v>0.2472263231475021</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>0.9512670565302144</v>
@@ -4128,39 +3803,39 @@
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.3283422830072888</v>
+        <v>-0.3372034926825385</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.0268209276442668</v>
+        <v>-0.03966012176582068</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.059745297335527</v>
+        <v>1.088345406940788</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.3283422830072888</v>
+        <v>-0.3372034926825385</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.6772718664109521</v>
+        <v>0.7177752927802767</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.09102914796604056</v>
+        <v>0.1173757526199353</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.260439275581632</v>
+        <v>1.335818324857759</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1055180017892465</v>
+        <v>-0.1166039321461161</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4169,110 +3844,48 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.1385354644109973</v>
+        <v>0.171220671088737</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.07306049421285321</v>
+        <v>0.1038660379375795</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.3381261530483139</v>
+        <v>-0.3380397400935387</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1790388907472599</v>
+        <v>0.1740509194643686</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2472263231475021</v>
+        <v>0.2513047692917923</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9512670565302144</v>
+        <v>0.9317738791423001</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.3372034926825385</v>
+        <v>-0.3340616179283677</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.03966012176582068</v>
+        <v>-0.03510779298083788</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.088345406940788</v>
+        <v>1.078204809253966</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.3372034926825385</v>
+        <v>-0.3340616179283675</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.7177752927802767</v>
+        <v>0.7587523149593043</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.1173757526199353</v>
+        <v>0.1440304211262609</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.335818324857759</v>
+        <v>1.41207876134175</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.1166039321461161</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0.171220671088737</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.1038660379375795</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-0.3380397400935387</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.1740509194643686</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.2513047692917923</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0.9317738791423001</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>-0.3340616179283677</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>-0.03510779298083788</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>1.078204809253966</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>-0.3340616179283675</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0.7587523149593043</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>0.1440304211262609</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>1.41207876134175</v>
-      </c>
-      <c r="R9" s="2" t="n">
         <v>-0.1136737333480079</v>
       </c>
     </row>
@@ -4287,7 +3900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4591,12 +4204,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4605,19 +4218,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-0.06676653353273054</v>
+        <v>-0.04941120899711726</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.06452511043579368</v>
+        <v>-0.04712810219865582</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.1513632279065376</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.06599576241334662</v>
+        <v>0.07294179359961758</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.2156952619322512</v>
+        <v>0.2326154609655196</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>1</v>
@@ -4626,39 +4239,39 @@
         <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.1513632279065376</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.13318215211393</v>
+        <v>0.09388774724005255</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.5391526104926985</v>
+        <v>0.6751222101795875</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.1208786768201607</v>
+        <v>-0.1513632279065376</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.06155253189821752</v>
+        <v>0.1201362258412626</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.1744708581765999</v>
+        <v>-0.1289125413411937</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.2152897169169782</v>
+        <v>0.4201954534641747</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.04770980148098947</v>
+        <v>-0.04910852885624428</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hrp</t>
+          <t>xgb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward</t>
+          <t>xgb_t_10_holdout</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4667,19 +4280,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.04941120899711726</v>
+        <v>-0.01500324256968033</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.04712810219865582</v>
+        <v>-0.01263749534581593</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.1891226670882522</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.07294179359961758</v>
+        <v>0.09328475897205027</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2326154609655196</v>
+        <v>0.3054222199740849</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1</v>
@@ -4688,39 +4301,39 @@
         <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.1891226670882522</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.09388774724005255</v>
+        <v>0.04521605491915381</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.6751222101795875</v>
+        <v>0.8435398396664642</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.1891226670882522</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.1201362258412626</v>
+        <v>0.214729672974497</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.1289125413411937</v>
+        <v>-0.05535080521648206</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.4201954534641747</v>
+        <v>0.7510509979475514</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.04910852885624428</v>
+        <v>-0.08996647052893747</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>xgb</t>
+          <t>rf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>xgb_t_10_holdout</t>
+          <t>rf_t_10_holdout</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4729,60 +4342,60 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.01500324256968033</v>
+        <v>0.009474010358029972</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.01263749534581593</v>
+        <v>0.01189854660096956</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.1891226670882522</v>
+        <v>-0.1965679708822623</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.09328475897205027</v>
+        <v>0.09228683758884382</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.3054222199740849</v>
+        <v>0.3142199894496041</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
+        <v>0.9772727272727273</v>
       </c>
       <c r="J7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.1891226670882522</v>
+        <v>-0.1965679708822623</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.04521605491915381</v>
+        <v>0.03561910265103974</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.8435398396664642</v>
+        <v>0.8767479710097934</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.1891226670882522</v>
+        <v>-0.1965679708822623</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.214729672974497</v>
+        <v>0.2564522869054031</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.05535080521648206</v>
+        <v>-0.02290471080472434</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.7510509979475514</v>
+        <v>0.8969824400054414</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.08996647052893747</v>
+        <v>-0.08406739461942148</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>lstm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rf_t_10_holdout</t>
+          <t>lstm_t_10_holdout_rank</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4791,110 +4404,48 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.009474010358029972</v>
+        <v>-0.01216599018987663</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.01189854660096956</v>
+        <v>-0.009793428505060708</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.1965679708822623</v>
+        <v>-0.1711634614757399</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.09228683758884382</v>
+        <v>0.0826181758453077</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.3142199894496041</v>
+        <v>0.2821735006319364</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9772727272727273</v>
+        <v>1</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.1965679708822623</v>
+        <v>-0.1711634614757399</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.03561910265103974</v>
+        <v>0.06836536404139437</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.8767479710097934</v>
+        <v>0.763436773988745</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.1965679708822623</v>
+        <v>-0.1711634614757399</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.2564522869054031</v>
+        <v>0.1918321211670491</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>-0.02290471080472434</v>
+        <v>-0.07315736280592</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.8969824400054414</v>
+        <v>0.6709631884831277</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.08406739461942148</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>lstm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lstm_t_10_holdout_rank</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>-0.01216599018987663</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>-0.009793428505060708</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-0.1711634614757399</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.0826181758453077</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.2821735006319364</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>-0.1711634614757399</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0.06836536404139437</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>0.763436773988745</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>-0.1711634614757399</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0.1918321211670491</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>-0.07315736280592</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.6709631884831277</v>
-      </c>
-      <c r="R9" s="2" t="n">
         <v>-0.07691029042613784</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_monthly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_monthly.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -680,27 +681,27 @@
         <v>0.7663835331252707</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="T3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -757,27 +758,27 @@
         <v>2.089923077804836</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
     </row>
@@ -834,27 +835,27 @@
         <v>1.295281120905988</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
     </row>
@@ -911,27 +912,27 @@
         <v>5.494242384343042</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -988,27 +989,27 @@
         <v>4.829376344876708</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="R7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
     </row>
@@ -1065,27 +1066,27 @@
         <v>3.360186480545662</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="R8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="T8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
     </row>
@@ -1232,28 +1233,28 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-0.09343144196767172</v>
+        <v>0.05644008609220919</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.2715577666208222</v>
+        <v>0.08831268540851216</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.1809616537571158</v>
+        <v>0.2970580221997946</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.9994459833795014</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="J2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.4704588408798223</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -1262,10 +1263,10 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.7119888462278816</v>
+        <v>0.2724034021441992</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -1274,7 +1275,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-0.1395291740668942</v>
+        <v>-0.08310591627222952</v>
       </c>
     </row>
     <row r="3">
@@ -1294,49 +1295,49 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.1379431368717021</v>
+        <v>0.0694524397980516</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.2552201670677432</v>
+        <v>0.0123171714867194</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-0.3927946397031032</v>
+        <v>-0.1698467665967934</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.1571171102885099</v>
+        <v>0.08752051030308652</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.1733782134839192</v>
+        <v>0.2968419789066029</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.9795013850415513</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.3653874450906897</v>
+        <v>-0.168347525660839</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.1984196959566027</v>
+        <v>0.001663465521344554</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>0.77666187419789</v>
+        <v>0.9918627307141473</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.3927946397031032</v>
+        <v>-0.1698467665967934</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.7931305141517735</v>
+        <v>0.2859367016828138</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.04739614285611493</v>
+        <v>0.01063601332392605</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>1.113964802052421</v>
+        <v>1.049681095875046</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.1397552035740055</v>
+        <v>-0.07520037734619367</v>
       </c>
     </row>
     <row r="4">
@@ -1356,49 +1357,49 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.1450386949103385</v>
+        <v>0.0446584681315485</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.05692592411839026</v>
+        <v>-0.01115218753601177</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.5405877541480402</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.3385720911587933</v>
+        <v>0.0887235763107324</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.1772354841845319</v>
+        <v>0.3128011051560898</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.9988919667590028</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="J4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.5206292358486946</v>
+        <v>-0.1706908012136737</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.0947431452773746</v>
+        <v>-0.001158835359547972</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1.106641411765261</v>
+        <v>1.005668741105609</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.5405877541480402</v>
+        <v>-0.1746123097224769</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.7835073997541646</v>
+        <v>0.2596730744822084</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.04177512819891538</v>
+        <v>-0.01000494626196236</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>1.100448980212525</v>
+        <v>0.9532666348445535</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.1420856921406376</v>
+        <v>-0.1039903280688754</v>
       </c>
     </row>
     <row r="5">
@@ -1418,49 +1419,49 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.3050913934539505</v>
+        <v>0.07488442474097812</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.4395948126489193</v>
+        <v>0.01745895379357942</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1109469294357623</v>
+        <v>0.07812037677756986</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1530752451527519</v>
+        <v>0.2757884445827267</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9518005540166204</v>
+        <v>0.9111111111111111</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2627477773058103</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.3922472502781837</v>
+        <v>0.01671906081640784</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.5584925916461387</v>
+        <v>0.918214415433338</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.770210184900723</v>
+        <v>0.2733293632849492</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.03400801284489896</v>
+        <v>0.0007277260805729213</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>1.081772824084672</v>
+        <v>1.003399227518678</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.1175306843923517</v>
+        <v>-0.05422944133655971</v>
       </c>
     </row>
     <row r="6">
@@ -1480,49 +1481,49 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.1727422704228461</v>
+        <v>0.03522731644179133</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.2936057179925118</v>
+        <v>-0.02007948195991338</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.3857020660410981</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1401986532528675</v>
+        <v>0.109751688353926</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1956510932256706</v>
+        <v>0.3134663783137708</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9722991689750693</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.368727712232564</v>
+        <v>-0.194516414529035</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.1921118441789917</v>
+        <v>-0.02985501211366604</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.7837618941180758</v>
+        <v>1.1460434676788</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.3857020660410981</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.8577439452797431</v>
+        <v>0.2852245968941696</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.08513787889039803</v>
+        <v>0.01007636000372569</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.204715424720587</v>
+        <v>1.047066940607384</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1370443733149529</v>
+        <v>-0.07773805881689089</v>
       </c>
     </row>
     <row r="7">
@@ -1542,49 +1543,49 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.2064468322738722</v>
+        <v>0.03447263601447603</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.3307838900705071</v>
+        <v>-0.02079384374649318</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.3957852429007654</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1429549412877313</v>
+        <v>0.1100517970205884</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2002183608269251</v>
+        <v>0.318256905013339</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9706371191135734</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.3754608976947176</v>
+        <v>-0.1959391460331659</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.1793967126992393</v>
+        <v>-0.03156858624818237</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.7980738484849268</v>
+        <v>1.154425856129244</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.3957852429007654</v>
+        <v>-0.1985517221071479</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.9317394664652177</v>
+        <v>0.2865601290137498</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.1283598434192632</v>
+        <v>0.011125973764055</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.308643346593946</v>
+        <v>1.051969713880653</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1397690308849029</v>
+        <v>-0.08580900226837973</v>
       </c>
     </row>
     <row r="8">
@@ -1604,49 +1605,49 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.2302139203155766</v>
+        <v>0.06813883782630481</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.3570004269569067</v>
+        <v>0.01107374841991238</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.4221174890977989</v>
+        <v>-0.1783245782924369</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1550900387558129</v>
+        <v>0.09453553638307291</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.1953067267187089</v>
+        <v>0.302310379654222</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.968421052631579</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.3976227638230778</v>
+        <v>-0.1729041606870662</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.137545638903235</v>
+        <v>-0.003824661998643064</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.8451807666733799</v>
+        <v>1.018709317512736</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.4221174890977989</v>
+        <v>-0.1783245782924369</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1.042264956961712</v>
+        <v>0.2914329719196807</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.1929195458612629</v>
+        <v>0.01495561057398431</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.463878208884358</v>
+        <v>1.069858047387411</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.1348418208118199</v>
+        <v>-0.0675906456116333</v>
       </c>
     </row>
   </sheetData>
@@ -1792,28 +1793,28 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.05390587101818811</v>
+        <v>-0.09123360655355661</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.2215345333965962</v>
+        <v>0.2716992530341495</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.2389368129070568</v>
+        <v>0.1810585772249194</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.9832848837209303</v>
+        <v>1</v>
       </c>
       <c r="J2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.503509252857314</v>
+        <v>-0.4707583434268612</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -1822,10 +1823,10 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>1.122709994261599</v>
+        <v>0.7171104771509156</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -1834,7 +1835,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-0.1530343433756423</v>
+        <v>-0.1395291740668942</v>
       </c>
     </row>
     <row r="3">
@@ -1854,49 +1855,49 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.0227461698863396</v>
+        <v>0.141755787534382</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.02956592423357962</v>
+        <v>0.2563798526971712</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-0.556246046224159</v>
+        <v>-0.3927946397031032</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.2474346419341499</v>
+        <v>0.1572040858054355</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.2562940218532995</v>
+        <v>0.1734718872117423</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.9934593023255814</v>
+        <v>0.9794786466999446</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.5562460462241589</v>
+        <v>-0.3641529320474194</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.1062190859957536</v>
+        <v>0.2014304997639758</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>1.104738479119449</v>
+        <v>0.7735453595927516</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.556246046224159</v>
+        <v>-0.3927946397031032</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1.304759565934982</v>
+        <v>0.7956452818298292</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.08576280894023403</v>
+        <v>0.04573660560805681</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>1.162151911538933</v>
+        <v>1.10951562859733</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.1639758006604788</v>
+        <v>-0.1397552035740055</v>
       </c>
     </row>
     <row r="4">
@@ -1916,49 +1917,49 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.2562066685833588</v>
+        <v>-0.1452922176580209</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.1919533832463862</v>
+        <v>-0.05948570666158792</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.4456113326384448</v>
+        <v>-0.5405877541480402</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.1643751024664248</v>
+        <v>0.3387400714875508</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.2154447623434743</v>
+        <v>0.1773285455590618</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.9491279069767442</v>
+        <v>0.9994453688297282</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.4375057689528338</v>
+        <v>-0.5219321743416376</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.1329400080149157</v>
+        <v>-0.0966927494825881</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.8689130665823445</v>
+        <v>1.108705095999487</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.4456113326384448</v>
+        <v>-0.5405877541480402</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>1.233279204028003</v>
+        <v>0.7878379101645963</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>0.05208870267973964</v>
+        <v>0.04118979760174413</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>1.098484212603029</v>
+        <v>1.098628363783892</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.1227419066313019</v>
+        <v>-0.1420856921406376</v>
       </c>
     </row>
     <row r="5">
@@ -1978,49 +1979,49 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.2553938843122963</v>
+        <v>0.3109354176354568</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.1911821718000761</v>
+        <v>0.442543900268815</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.343246110573307</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1742196764528615</v>
+        <v>0.1110081735734261</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.2118070551778035</v>
+        <v>0.1531549489989729</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9491279069767442</v>
+        <v>0.9517470881863561</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.4557974809248456</v>
+        <v>-0.2609524087912378</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.09609800828525117</v>
+        <v>0.3964274769943947</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.9052415190749453</v>
+        <v>0.5543234919463098</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.343246110573307</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>1.306850557115716</v>
+        <v>0.7738173200609908</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>0.08674786633685749</v>
+        <v>0.03302457451902874</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>1.164014361496109</v>
+        <v>1.079076857355887</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.1243810385007439</v>
+        <v>-0.1175306843923517</v>
       </c>
     </row>
     <row r="6">
@@ -2040,49 +2041,49 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.03069342544864184</v>
+        <v>0.1701807858124662</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.08027215598020898</v>
+        <v>0.2876585162602945</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.6157753345140465</v>
+        <v>-0.385702066041098</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.2834217467647488</v>
+        <v>0.1402763471638039</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2902475246683776</v>
+        <v>0.1957580265743671</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
+        <v>0.9728230726566833</v>
       </c>
       <c r="J6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.6131881355073265</v>
+        <v>-0.3701203966363428</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.2209082108402154</v>
+        <v>0.1901549992155818</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.217828931698091</v>
+        <v>0.78622163962527</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.6157753345140465</v>
+        <v>-0.385702066041098</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1.50588635853417</v>
+        <v>0.8577848521582769</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.1805128186650207</v>
+        <v>0.08192505775212133</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.341295941276967</v>
+        <v>1.196168344334142</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1991621896471399</v>
+        <v>-0.1370443733149529</v>
       </c>
     </row>
     <row r="7">
@@ -2102,49 +2103,49 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.05847752440067311</v>
+        <v>0.2071638246975345</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.1066351355555943</v>
+        <v>0.3283543861249494</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.6100001664268992</v>
+        <v>-0.3957852429007653</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.2927826980910351</v>
+        <v>0.1430341619260324</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2857263117276639</v>
+        <v>0.2003292571814022</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
+        <v>0.971159179145868</v>
       </c>
       <c r="J7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.6055610031715249</v>
+        <v>-0.3754722955855372</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.205546127297479</v>
+        <v>0.1800426074891857</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.202680982991053</v>
+        <v>0.7975903153458862</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.6100001664268992</v>
+        <v>-0.3957852429007653</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>1.386991355240556</v>
+        <v>0.9329227769476338</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.1245018686930377</v>
+        <v>0.1256834098146096</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.23539592800434</v>
+        <v>1.300947073948971</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1935283927621277</v>
+        <v>-0.1397690308849029</v>
       </c>
     </row>
     <row r="8">
@@ -2164,49 +2165,49 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.07923416091300595</v>
+        <v>0.236616904435895</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.1263300979645993</v>
+        <v>0.3607643431290386</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.6146619938319893</v>
+        <v>-0.4221174890977989</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.3064991258757455</v>
+        <v>0.1551756964035938</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2922276320458878</v>
+        <v>0.1954076414005457</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
+        <v>0.9683860232945092</v>
       </c>
       <c r="J8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.6131081926512691</v>
+        <v>-0.3950032996914198</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.2207471950377711</v>
+        <v>0.1431388531015461</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.217670160323774</v>
+        <v>0.8390787018579714</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.6146619938319893</v>
+        <v>-0.4221174890977989</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1.379905238616354</v>
+        <v>1.044006031446378</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.1211636281216184</v>
+        <v>0.1903753769168413</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.229084309990409</v>
+        <v>1.455851036501685</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.2037181450170952</v>
+        <v>-0.1348418208118199</v>
       </c>
     </row>
   </sheetData>
@@ -2352,28 +2353,28 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.02340987064093203</v>
+        <v>0.05390587101818811</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.0812675747870259</v>
+        <v>0.2215345333965962</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.2145128387962869</v>
+        <v>0.2389368129070568</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9832848837209303</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.1954368693665688</v>
+        <v>-0.503509252857314</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -2382,10 +2383,10 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.2720069211165606</v>
+        <v>1.122709994261599</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -2394,7 +2395,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-0.03286068493604632</v>
+        <v>-0.1530343433756423</v>
       </c>
     </row>
     <row r="3">
@@ -2414,49 +2415,49 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.02739809264358484</v>
+        <v>0.0227461698863396</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.00389699388003284</v>
+        <v>-0.02956592423357962</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-0.1661942153206122</v>
+        <v>-0.556246046224159</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.05467802782354099</v>
+        <v>0.2474346419341499</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.1825167764355579</v>
+        <v>0.2562940218532995</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.9241379310344827</v>
+        <v>0.9934593023255814</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.1661942153206122</v>
+        <v>-0.5562460462241589</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.03634600310721914</v>
+        <v>-0.1062190859957536</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>0.8503728895129404</v>
+        <v>1.104738479119449</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.1661942153206122</v>
+        <v>-0.556246046224159</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.2321791375417674</v>
+        <v>1.304759565934982</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>-0.03131098024201984</v>
+        <v>0.08576280894023403</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.8535780508403825</v>
+        <v>1.162151911538933</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.02614394426954236</v>
+        <v>-0.1639758006604788</v>
       </c>
     </row>
     <row r="4">
@@ -2476,49 +2477,49 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.004825376533324266</v>
+        <v>0.2562066685833588</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.02758938328059446</v>
+        <v>0.1919533832463862</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.1989196555792887</v>
+        <v>-0.4456113326384448</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.0814304948965289</v>
+        <v>0.1643751024664248</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.2145551922699243</v>
+        <v>0.2154447623434743</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.9862068965517241</v>
+        <v>0.9491279069767442</v>
       </c>
       <c r="J4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.1972404039901224</v>
+        <v>-0.4375057689528338</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.002241632203719979</v>
+        <v>0.1329400080149157</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1.009228221007628</v>
+        <v>0.8689130665823445</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.1989196555792887</v>
+        <v>-0.4456113326384448</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.2396919680726315</v>
+        <v>1.233279204028003</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>-0.02540469906843212</v>
+        <v>0.05208870267973964</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.8811980485228851</v>
+        <v>1.098484212603029</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.03283823425413634</v>
+        <v>-0.1227419066313019</v>
       </c>
     </row>
     <row r="5">
@@ -2538,49 +2539,49 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.0189637709832835</v>
+        <v>0.2553938843122963</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.004344397865602034</v>
+        <v>0.1911821718000761</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.04520489920804412</v>
+        <v>0.1742196764528615</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.165114162844639</v>
+        <v>0.2118070551778035</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9448275862068966</v>
+        <v>0.9491279069767442</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.4557974809248456</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.06570035000010499</v>
+        <v>0.09609800828525117</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.7295286224594077</v>
+        <v>0.9052415190749453</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.1884023656024003</v>
+        <v>1.306850557115716</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.06572649419295029</v>
+        <v>0.08674786633685749</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.6926381315189625</v>
+        <v>1.164014361496109</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.02330447460112961</v>
+        <v>-0.1243810385007439</v>
       </c>
     </row>
     <row r="6">
@@ -2600,49 +2601,49 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.03113418626728315</v>
+        <v>-0.03069342544864184</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.007547626662535167</v>
+        <v>-0.08027215598020898</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.05957889510636127</v>
+        <v>0.2834217467647488</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.1870865456402408</v>
+        <v>0.2902475246683776</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9379310344827586</v>
+        <v>1</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.6131881355073265</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.01865603812212591</v>
+        <v>-0.2209082108402154</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.9231979079208384</v>
+        <v>1.217828931698091</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.2581357263948778</v>
+        <v>1.50588635853417</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.01090496796157892</v>
+        <v>0.1805128186650207</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.9490042581830531</v>
+        <v>1.341295941276967</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.0280449453540883</v>
+        <v>-0.1991621896471399</v>
       </c>
     </row>
     <row r="7">
@@ -2662,49 +2663,49 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.05464279041512032</v>
+        <v>-0.05847752440067311</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.03051848596557694</v>
+        <v>-0.1066351355555943</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.05565303537278199</v>
+        <v>0.2927826980910351</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.1949988330089462</v>
+        <v>0.2857263117276639</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.896551724137931</v>
+        <v>1</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.1756429698727684</v>
+        <v>-0.6055610031715249</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.02460204642762664</v>
+        <v>-0.205546127297479</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.8987197269483773</v>
+        <v>1.202680982991053</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.1758389292270287</v>
+        <v>-0.6100001664268992</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.279351969925393</v>
+        <v>1.386991355240556</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.005774378021768278</v>
+        <v>0.1245018686930377</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.027003168811594</v>
+        <v>1.23539592800434</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.02998688672969829</v>
+        <v>-0.1935283927621277</v>
       </c>
     </row>
     <row r="8">
@@ -2724,49 +2725,49 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.05461060122071615</v>
+        <v>-0.07923416091300595</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.03048703307917489</v>
+        <v>-0.1263300979645993</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.161539993759288</v>
+        <v>-0.6146619938319893</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.04772879566569357</v>
+        <v>0.3064991258757455</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.1794422862086121</v>
+        <v>0.2922276320458878</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.8689655172413793</v>
+        <v>1</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.161539993759288</v>
+        <v>-0.6131081926512691</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.0421307841692844</v>
+        <v>-0.2207471950377711</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.8265584394738612</v>
+        <v>1.217670160323774</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.161539993759288</v>
+        <v>-0.6146619938319893</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.2577947586899569</v>
+        <v>1.379905238616354</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>-0.01117302287485056</v>
+        <v>0.1211636281216184</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.9477507323406914</v>
+        <v>1.229084309990409</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.0232535172924333</v>
+        <v>-0.2037181450170952</v>
       </c>
     </row>
   </sheetData>
@@ -2912,28 +2913,28 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.09782647207714601</v>
+        <v>0.01891210187562598</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.2022979914860074</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.1130717188570335</v>
+        <v>0.08099293800752018</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.459050197355985</v>
+        <v>0.2138559415886583</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.9098360655737705</v>
+        <v>0.9657534246575342</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.2902196151348786</v>
+        <v>-0.1989728318606706</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -2942,10 +2943,10 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.2022979914860074</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.5467128924473792</v>
+        <v>0.2720069211165606</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -2954,7 +2955,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-0.05185156587886086</v>
+        <v>-0.03286068493604632</v>
       </c>
     </row>
     <row r="3">
@@ -2974,49 +2975,49 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.009671312777262075</v>
+        <v>0.02592301548596776</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.08029972089586224</v>
+        <v>0.00688078353121524</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-0.3081513905894094</v>
+        <v>-0.1673913441411503</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.1274648202199045</v>
+        <v>0.05551001845813486</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.4586199334254946</v>
+        <v>0.1818988201545211</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.9836065573770492</v>
+        <v>0.9315068493150684</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.3081513905894094</v>
+        <v>-0.1673913441411503</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-0.0252638363033072</v>
+        <v>0.03942623793008115</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>1.061786917628559</v>
+        <v>0.8412773873488667</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.3081513905894094</v>
+        <v>-0.1673913441411503</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.4593818633782261</v>
+        <v>0.2321791375417674</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>-0.05646233990522209</v>
+        <v>-0.03131098024201984</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.8402616249303857</v>
+        <v>0.8535780508403825</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.07649568993169786</v>
+        <v>-0.02614394426954236</v>
       </c>
     </row>
     <row r="4">
@@ -3036,49 +3037,49 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.03655092770721002</v>
+        <v>-0.00716512238730771</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.05581532776669107</v>
+        <v>-0.0255932030004653</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.3158142431874948</v>
+        <v>-0.1991277646524821</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.1254404790617945</v>
+        <v>0.08136015489054858</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.4644648305065673</v>
+        <v>0.2138357999046741</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.9508196721311475</v>
+        <v>1</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.315814243187495</v>
+        <v>-0.1991277646524821</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-0.03605992585647466</v>
+        <v>-0.0001934176492057738</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1.088190551974653</v>
+        <v>1.00077866304843</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.3158142431874948</v>
+        <v>-0.1991277646524821</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.5150138940867595</v>
+        <v>0.2396919680726315</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>-0.02049442951914759</v>
+        <v>-0.02540469906843212</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.9420189302309699</v>
+        <v>0.8811980485228851</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.06320652629413515</v>
+        <v>-0.03283823425413634</v>
       </c>
     </row>
     <row r="5">
@@ -3098,49 +3099,49 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-0.0009544101684616502</v>
+        <v>0.01970412365980478</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.08997859384708495</v>
+        <v>0.0007773210100467942</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1452798889626854</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1202708276706985</v>
+        <v>0.04505087866076889</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.428252010780779</v>
+        <v>0.1645456863596117</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>0.9383561643835616</v>
       </c>
       <c r="J5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1419538085967058</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-0.00807433626786469</v>
+        <v>0.07118238373413943</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.019747133566668</v>
+        <v>0.7134331218450367</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1452798889626854</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.4189993189650008</v>
+        <v>0.1884023656024003</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.08257096330288938</v>
+        <v>-0.06572649419295029</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.7663973627717755</v>
+        <v>0.6926381315189625</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.07538615706116925</v>
+        <v>-0.02330447460112961</v>
       </c>
     </row>
     <row r="6">
@@ -3160,49 +3161,49 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.004064398596093755</v>
+        <v>0.02795562822442021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.08540700726923578</v>
+        <v>0.008875668796304303</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.1829533120643722</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1330355594692814</v>
+        <v>0.06157120174811177</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.4884782875332566</v>
+        <v>0.1864906684214894</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9918032786885246</v>
+        <v>0.952054794520548</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.1829533120643722</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.04551457597582553</v>
+        <v>0.01999872218255661</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.111313472861166</v>
+        <v>0.9194889088802032</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.1829533120643722</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.4820684921877625</v>
+        <v>0.2581357263948778</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.04179469931056778</v>
+        <v>-0.01090496796157892</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.8817580467688738</v>
+        <v>0.9490042581830531</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.09007578809896477</v>
+        <v>-0.0280449453540883</v>
       </c>
     </row>
     <row r="7">
@@ -3222,49 +3223,49 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-0.03121918450036776</v>
+        <v>0.05118637363330114</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.1175464974290086</v>
+        <v>0.031675226644442</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.1783446632793302</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1525896620499075</v>
+        <v>0.05752531060341064</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.507010924502074</v>
+        <v>0.194384405087508</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1</v>
+        <v>0.9041095890410958</v>
       </c>
       <c r="J7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.1783446632793301</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.07186081874535022</v>
+        <v>0.02575214599681663</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.175747595702974</v>
+        <v>0.8963267075789259</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.341225014720676</v>
+        <v>-0.1783446632793302</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.4705792374445794</v>
+        <v>0.279351969925393</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.04922287476529197</v>
+        <v>0.005774378021768278</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.8607428943883418</v>
+        <v>1.027003168811594</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.09590060655538413</v>
+        <v>-0.02998688672969829</v>
       </c>
     </row>
     <row r="8">
@@ -3284,49 +3285,49 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.00261610496364173</v>
+        <v>0.05267606622749588</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.09149221629784987</v>
+        <v>0.03313726894568902</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.3207580395918463</v>
+        <v>-0.1630780308514724</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1344899709337924</v>
+        <v>0.04874012228299625</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.4858267016059757</v>
+        <v>0.1788458642458411</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
+        <v>0.8767123287671232</v>
       </c>
       <c r="J8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.3207580395918463</v>
+        <v>-0.1630780308514724</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.04302517385398152</v>
+        <v>0.04481096576608823</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.105225225534033</v>
+        <v>0.8195994866558804</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.3207580395918463</v>
+        <v>-0.1630780308514724</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.468377917107822</v>
+        <v>0.2577947586899569</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>-0.05064609968796929</v>
+        <v>-0.01117302287485056</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.8567164293695581</v>
+        <v>0.9477507323406914</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.09945162290284171</v>
+        <v>-0.0232535172924333</v>
       </c>
     </row>
   </sheetData>
@@ -3472,28 +3473,28 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.06101703543393744</v>
+        <v>0.1113578145363066</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.3239608533428741</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.1799741913752891</v>
+        <v>0.1112768582964018</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.240579627043532</v>
+        <v>0.4518304992174232</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.9746588693957114</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>-0.3098313187450097</v>
+        <v>-0.2902196151348786</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -3502,10 +3503,10 @@
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0.3098313187450098</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.5373300241682992</v>
+        <v>0.5657770181230022</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -3514,7 +3515,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>-0.1055402030174765</v>
+        <v>-0.05185156587886086</v>
       </c>
     </row>
     <row r="3">
@@ -3534,49 +3535,49 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.08979519153768911</v>
+        <v>0.008880887124637526</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.02712318006466496</v>
+        <v>-0.09220876127498656</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-0.291261694520513</v>
+        <v>-0.3081513905894094</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.14818051735273</v>
+        <v>0.1254423205444389</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.2071327226944866</v>
+        <v>0.4512557897110157</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.9532163742690059</v>
+        <v>0.9841269841269841</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>-0.2912616945205131</v>
+        <v>-0.3081513905894094</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.02690592130423819</v>
+        <v>-0.0252638363033072</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>0.940065373959889</v>
+        <v>1.061786917628559</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.291261694520513</v>
+        <v>-0.3081513905894094</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.5376552715044851</v>
+        <v>0.4582393798321538</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.0002115663722639383</v>
+        <v>-0.06868004642178283</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>1.000605302740507</v>
+        <v>0.8099292922013505</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>-0.08751825522014978</v>
+        <v>-0.07649568993169786</v>
       </c>
     </row>
     <row r="4">
@@ -3596,49 +3597,49 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.09002986682938641</v>
+        <v>0.04823577932436307</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.02734435963470006</v>
+        <v>-0.05679722082872107</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.2867967086275238</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.1603957635724635</v>
+        <v>0.1234492339101719</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.2069006720189944</v>
+        <v>0.4570755476210876</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.9629629629629629</v>
+        <v>0.9206349206349206</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>-0.2829863495851492</v>
+        <v>-0.315814243187495</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.03889624361257016</v>
+        <v>-0.03605992585647466</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0.9133561795218198</v>
+        <v>1.088190551974653</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.2829863495851492</v>
+        <v>-0.3158142431874948</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.5202358646850243</v>
+        <v>0.5320923724105275</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>-0.01111938179476002</v>
+        <v>-0.02151305410833948</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.9681868521869144</v>
+        <v>0.9404630364375255</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>-0.1022317316320518</v>
+        <v>-0.06320652629413515</v>
       </c>
     </row>
     <row r="5">
@@ -3658,49 +3659,49 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.05550959933794908</v>
+        <v>0.001402698831345583</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.005190714109256422</v>
+        <v>-0.09893763670599443</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1161134555088488</v>
+        <v>0.1183626651723915</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.1734081721485486</v>
+        <v>0.4213989939818436</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.9727095516569201</v>
+        <v>0.9920634920634921</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>-0.2377598766809244</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.1044258367867865</v>
+        <v>-0.00807433626786469</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.7673849036436503</v>
+        <v>1.019747133566668</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.3847468363930642</v>
+        <v>0.4223472503301919</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.09925207039248651</v>
+        <v>-0.09160293332491798</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.7160345022383415</v>
+        <v>0.7464906434894674</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>-0.07769789874505417</v>
+        <v>-0.07538615706116925</v>
       </c>
     </row>
     <row r="6">
@@ -3720,49 +3721,49 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.1265525925696835</v>
+        <v>-0.005339347390854843</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.06176673413065714</v>
+        <v>-0.1050041313434693</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-0.3287615049188402</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.1723102832459509</v>
+        <v>0.1309299660066359</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.2353745170087453</v>
+        <v>0.4806983762937558</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.9512670565302144</v>
+        <v>0.9920634920634921</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>-0.3283422830072888</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-0.0268209276442668</v>
+        <v>-0.04551457597582553</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.059745297335527</v>
+        <v>1.111313472861166</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.3283422830072888</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.6772718664109521</v>
+        <v>0.4681879127595099</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>0.09102914796604056</v>
+        <v>-0.06232631098422858</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>1.260439275581632</v>
+        <v>0.8275131328464882</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>-0.1055180017892465</v>
+        <v>-0.09007578809896477</v>
       </c>
     </row>
     <row r="7">
@@ -3782,49 +3783,49 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.1385354644109973</v>
+        <v>-0.03998309990267035</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.07306049421285321</v>
+        <v>-0.1361765872876155</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-0.3381261530483139</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.1790388907472599</v>
+        <v>0.1503162255013063</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2472263231475021</v>
+        <v>0.4989097639400619</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9512670565302144</v>
+        <v>1</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-0.3372034926825385</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-0.03966012176582068</v>
+        <v>-0.07186081874535022</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.088345406940788</v>
+        <v>1.175747595702974</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.3372034926825385</v>
+        <v>-0.341225014720676</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.7177752927802767</v>
+        <v>0.4572758856201522</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.1173757526199353</v>
+        <v>-0.06929539215802083</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>1.335818324857759</v>
+        <v>0.8082263347090188</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>-0.1166039321461161</v>
+        <v>-0.09590060655538413</v>
       </c>
     </row>
     <row r="8">
@@ -3844,49 +3845,49 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.171220671088737</v>
+        <v>-0.01373903328845372</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.1038660379375795</v>
+        <v>-0.1125621705165718</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-0.3380397400935387</v>
+        <v>-0.3207580395918463</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.1740509194643686</v>
+        <v>0.1323679496907128</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2513047692917923</v>
+        <v>0.4781070119682687</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.9317738791423001</v>
+        <v>1</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-0.3340616179283677</v>
+        <v>-0.3207580395918463</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-0.03510779298083788</v>
+        <v>-0.04302517385398152</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.078204809253966</v>
+        <v>1.105225225534033</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.3340616179283675</v>
+        <v>-0.3207580395918463</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.7587523149593043</v>
+        <v>0.4520024147490922</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>0.1440304211262609</v>
+        <v>-0.07266334992596768</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.41207876134175</v>
+        <v>0.7989055763499129</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>-0.1136737333480079</v>
+        <v>-0.09945162290284171</v>
       </c>
     </row>
   </sheetData>
@@ -4032,25 +4033,585 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-0.002396027003975565</v>
+        <v>0.06101703543393744</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
+        <v>-0.3239608533428741</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.1799741913752891</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0.240579627043532</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0.9746588693957114</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>-0.3098313187450097</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>-0.3098313187450098</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.5373300241682992</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>-0.1055402030174765</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>equal_weight</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>equal_t_10</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.08979519153768911</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.02712318006466496</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>-0.291261694520513</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.14818051735273</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0.2071327226944866</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0.9532163742690059</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>-0.2912616945205131</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0.02690592130423819</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>0.940065373959889</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>-0.291261694520513</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.5376552715044851</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>0.0002115663722639383</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>1.000605302740507</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>-0.08751825522014978</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mvo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>mvo_t_10_lw</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.09002986682938641</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.02734435963470006</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-0.2867967086275238</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.1603957635724635</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.2069006720189944</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>-0.2829863495851492</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0.03889624361257016</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0.9133561795218198</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>-0.2829863495851492</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0.5202358646850243</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>-0.01111938179476002</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.9681868521869144</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>-0.1022317316320518</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.05550959933794908</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>-0.005190714109256422</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-0.2377598766809245</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.1161134555088488</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.1734081721485486</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0.9727095516569201</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>-0.2377598766809244</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0.1044258367867865</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0.7673849036436503</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>-0.2377598766809245</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0.3847468363930642</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>-0.09925207039248651</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.7160345022383415</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>-0.07769789874505417</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.1265525925696835</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.06176673413065714</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-0.3287615049188402</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.1723102832459509</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.2353745170087453</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0.9512670565302144</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>-0.3283422830072888</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>-0.0268209276442668</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>1.059745297335527</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>-0.3283422830072888</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.6772718664109521</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0.09102914796604056</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>1.260439275581632</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>-0.1055180017892465</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rf_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.1385354644109973</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.07306049421285321</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-0.3381261530483139</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.1790388907472599</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.2472263231475021</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0.9512670565302144</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>-0.3372034926825385</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>-0.03966012176582068</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>1.088345406940788</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>-0.3372034926825385</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.7177752927802767</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>0.1173757526199353</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>1.335818324857759</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>-0.1166039321461161</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>lstm_t_10_holdout_rank</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.171220671088737</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.1038660379375795</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-0.3380397400935387</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.1740509194643686</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.2513047692917923</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.9317738791423001</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>-0.3340616179283677</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>-0.03510779298083788</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>1.078204809253966</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-0.3340616179283675</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.7587523149593043</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.1440304211262609</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>1.41207876134175</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>-0.1136737333480079</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>full_cum_return</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>full_excess_return</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>full_max_dd</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_ann_vol</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>full_underwater_share</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>full_recovered</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_cum_return</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_excess_return</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_down_capture</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cum_return</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_excess_return</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_recovery_capture</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_max_dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.004925019651871976</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>-0.2242012270138081</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.1038210158252798</v>
+        <v>0.1032426212645823</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.3353086213004998</v>
+        <v>0.3336266559947869</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
+        <v>0.9887640449438202</v>
       </c>
       <c r="J2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>-0.2242012270138081</v>
@@ -4065,7 +4626,7 @@
         <v>-0.2242012270138081</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.2859055823922789</v>
+        <v>0.2953423679490121</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
@@ -4094,19 +4655,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>-0.01305486510854659</v>
+        <v>-0.008355480381121327</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.01068443830727761</v>
+        <v>-0.013215413860025</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>-0.1872487154673582</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.08675628479577806</v>
+        <v>0.08627745467977051</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.2857163297587581</v>
+        <v>0.2842079090488103</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>1</v>
@@ -4127,13 +4688,13 @@
         <v>-0.1872487154673582</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.2143261458626655</v>
+        <v>0.2201082157490606</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>-0.05566461294650271</v>
+        <v>-0.05808051528421321</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.7496395980425373</v>
+        <v>0.7452646136671459</v>
       </c>
       <c r="R3" s="2" t="n">
         <v>-0.06639663516197625</v>
@@ -4156,19 +4717,19 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>-0.02332536918041006</v>
+        <v>-0.02255028811919957</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.02097960988825964</v>
+        <v>-0.0273406545103132</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>-0.1919673527633516</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.09542986630280144</v>
+        <v>0.0949279844316521</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.2710807151579593</v>
+        <v>0.2695420012099382</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>1</v>
@@ -4189,13 +4750,13 @@
         <v>-0.1919673527633516</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.2085857611200868</v>
+        <v>0.2095448849723227</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>-0.06012869244128138</v>
+        <v>-0.06623537151227232</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.729561694370469</v>
+        <v>0.7094982221057377</v>
       </c>
       <c r="R4" s="2" t="n">
         <v>-0.04392141022055807</v>
@@ -4218,19 +4779,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-0.04941120899711726</v>
+        <v>-0.04521242326464603</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.04712810219865582</v>
+        <v>-0.04989172518949392</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>-0.1513632279065376</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.07294179359961758</v>
+        <v>0.07269182521527755</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.2326154609655196</v>
+        <v>0.2314419517208828</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>1</v>
@@ -4251,13 +4812,13 @@
         <v>-0.1513632279065376</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>0.1201362258412626</v>
+        <v>0.1250839088436306</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-0.1289125413411937</v>
+        <v>-0.1314389641828525</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.4201954534641747</v>
+        <v>0.4235217239987224</v>
       </c>
       <c r="R5" s="2" t="n">
         <v>-0.04910852885624428</v>
@@ -4280,19 +4841,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>-0.01500324256968033</v>
+        <v>-0.01015087478268217</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.01263749534581593</v>
+        <v>-0.0150020092442088</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>-0.1891226670882522</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.09328475897205027</v>
+        <v>0.09277123339370263</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.3054222199740849</v>
+        <v>0.3038024735945229</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>1</v>
@@ -4313,13 +4874,13 @@
         <v>-0.1891226670882522</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>0.214729672974497</v>
+        <v>0.220713768953076</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>-0.05535080521648206</v>
+        <v>-0.05761303022466546</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.7510509979475514</v>
+        <v>0.7473149568272576</v>
       </c>
       <c r="R6" s="2" t="n">
         <v>-0.08996647052893747</v>
@@ -4342,22 +4903,22 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.009474010358029972</v>
+        <v>0.01313097569578958</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.01189854660096956</v>
+        <v>0.008165739615837442</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>-0.1965679708822623</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.09228683758884382</v>
+        <v>0.09177270078849505</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.3142199894496041</v>
+        <v>0.3124853358722013</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.9772727272727273</v>
+        <v>0.9662921348314607</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -4375,13 +4936,13 @@
         <v>-0.1965679708822623</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.2564522869054031</v>
+        <v>0.2610039667055915</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>-0.02290471080472434</v>
+        <v>-0.02650913155708057</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.8969824400054414</v>
+        <v>0.8837335750983453</v>
       </c>
       <c r="R7" s="2" t="n">
         <v>-0.08406739461942148</v>
@@ -4404,19 +4965,19 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-0.01216599018987663</v>
+        <v>-0.006399259684120362</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.009793428505060708</v>
+        <v>-0.01126878037121148</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>-0.1711634614757399</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.0826181758453077</v>
+        <v>0.08216067292169081</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.2821735006319364</v>
+        <v>0.2807448381846609</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>1</v>
@@ -4437,13 +4998,13 @@
         <v>-0.1711634614757399</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.1918321211670491</v>
+        <v>0.1987897421667504</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>-0.07315736280592</v>
+        <v>-0.07453830598866218</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.6709631884831277</v>
+        <v>0.6730823740164141</v>
       </c>
       <c r="R8" s="2" t="n">
         <v>-0.07691029042613784</v>
